--- a/data/trans_orig/P04B1_1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023</t>
+          <t>Población según si su vivienda tiene una temperatura suficientemente cálida durante los meses fríos en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>325474</t>
+          <t>325718</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>370271</t>
+          <t>367587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>310857</t>
+          <t>310944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>341993</t>
+          <t>343489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>647842</t>
+          <t>646663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>700857</t>
+          <t>700129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133402</t>
+          <t>136086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178199</t>
+          <t>177955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101551</t>
+          <t>100055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132687</t>
+          <t>132600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246360</t>
+          <t>247088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>299375</t>
+          <t>300554</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>305127</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>342299</t>
+          <t>341686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239807</t>
+          <t>239198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>271382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>555983</t>
+          <t>554215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>603229</t>
+          <t>604901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,6%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108309</t>
+          <t>108922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147052</t>
+          <t>145481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111660</t>
+          <t>111198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142773</t>
+          <t>143382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>228287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>277205</t>
+          <t>278973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>445299</t>
+          <t>444273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>618338</t>
+          <t>617468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103178</t>
+          <t>102177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122274</t>
+          <t>121417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>556624</t>
+          <t>557112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>753673</t>
+          <t>748570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222965</t>
+          <t>223991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63077</t>
+          <t>64078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80846</t>
+          <t>85949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277895</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>676230</t>
+          <t>676988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>737872</t>
+          <t>741394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>696361</t>
+          <t>697016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>866009</t>
+          <t>870025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1394484</t>
+          <t>1388738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1645133</t>
+          <t>1643655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296167</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357809</t>
+          <t>357051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111278</t>
+          <t>107262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>280926</t>
+          <t>280271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366193</t>
+          <t>367671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>616842</t>
+          <t>622588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>282903</t>
+          <t>283145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>327643</t>
+          <t>326710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>513532</t>
+          <t>511508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>635877</t>
+          <t>627954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>808843</t>
+          <t>808744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>935708</t>
+          <t>930972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146373</t>
+          <t>147306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191113</t>
+          <t>190871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204099</t>
+          <t>212022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>326444</t>
+          <t>328468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378284</t>
+          <t>383020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505149</t>
+          <t>505248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159697</t>
+          <t>158509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>199015</t>
+          <t>199605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>444733</t>
+          <t>445776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>496054</t>
+          <t>496679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>619974</t>
+          <t>622306</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>685597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41328</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264716</t>
+          <t>264091</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316037</t>
+          <t>314994</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>318102</t>
+          <t>315516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>381139</t>
+          <t>378807</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2301195</t>
+          <t>2301799</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2602352</t>
+          <t>2638272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2385528</t>
+          <t>2386584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2675707</t>
+          <t>2697624</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4717340</t>
+          <t>4721623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5176428</t>
+          <t>5134509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>768590</t>
+          <t>732670</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1069747</t>
+          <t>1069143</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>894706</t>
+          <t>872789</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1184885</t>
+          <t>1183829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1764927</t>
+          <t>1806846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2224015</t>
+          <t>2219732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B1_1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B1_1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>346970</t>
+          <t>375394</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>325718</t>
+          <t>350959</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>367587</t>
+          <t>395723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>327073</t>
+          <t>354270</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>310944</t>
+          <t>335280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>343489</t>
+          <t>370936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>674044</t>
+          <t>729664</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>646663</t>
+          <t>700402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>700129</t>
+          <t>756164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>156703</t>
+          <t>173656</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136086</t>
+          <t>153327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177955</t>
+          <t>198091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>116471</t>
+          <t>130154</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100055</t>
+          <t>113488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132600</t>
+          <t>149144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>273173</t>
+          <t>303810</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247088</t>
+          <t>277310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300554</t>
+          <t>333072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503673</t>
+          <t>549050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503673</t>
+          <t>549050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503673</t>
+          <t>549050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>443544</t>
+          <t>484424</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>443544</t>
+          <t>484424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>443544</t>
+          <t>484424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>947217</t>
+          <t>1033474</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>947217</t>
+          <t>1033474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>947217</t>
+          <t>1033474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>324097</t>
+          <t>339651</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>305127</t>
+          <t>317813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>341686</t>
+          <t>359401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>255557</t>
+          <t>283074</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239198</t>
+          <t>266783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>271382</t>
+          <t>298694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>579654</t>
+          <t>622725</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>554215</t>
+          <t>592015</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>604901</t>
+          <t>647717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>126511</t>
+          <t>141826</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108922</t>
+          <t>122076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145481</t>
+          <t>163664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>127023</t>
+          <t>140069</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>111198</t>
+          <t>124449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143382</t>
+          <t>156360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>253534</t>
+          <t>281895</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228287</t>
+          <t>256903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278973</t>
+          <t>312605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>450608</t>
+          <t>481477</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>450608</t>
+          <t>481477</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>450608</t>
+          <t>481477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833188</t>
+          <t>904620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833188</t>
+          <t>904620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833188</t>
+          <t>904620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>531665</t>
+          <t>316737</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>444273</t>
+          <t>294926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>617468</t>
+          <t>337568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113177</t>
+          <t>126663</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102177</t>
+          <t>114885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121417</t>
+          <t>136533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>644842</t>
+          <t>443400</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557112</t>
+          <t>418047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>748570</t>
+          <t>464974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>136599</t>
+          <t>154875</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50796</t>
+          <t>134044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>223991</t>
+          <t>176686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53078</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44838</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64078</t>
+          <t>71905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>189677</t>
+          <t>215002</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85949</t>
+          <t>193428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277407</t>
+          <t>240355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>708277</t>
+          <t>761607</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>676988</t>
+          <t>724939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>741394</t>
+          <t>794733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>762033</t>
+          <t>606526</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>697016</t>
+          <t>580954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>870025</t>
+          <t>629635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1470311</t>
+          <t>1368134</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1388738</t>
+          <t>1324788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1643655</t>
+          <t>1407900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>325762</t>
+          <t>369233</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292645</t>
+          <t>336107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357051</t>
+          <t>405901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>215254</t>
+          <t>253026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107262</t>
+          <t>229917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>280271</t>
+          <t>278598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>541015</t>
+          <t>622258</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367671</t>
+          <t>582492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>622588</t>
+          <t>665604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034039</t>
+          <t>1130840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034039</t>
+          <t>1130840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034039</t>
+          <t>1130840</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977287</t>
+          <t>859552</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977287</t>
+          <t>859552</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977287</t>
+          <t>859552</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011326</t>
+          <t>1990392</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011326</t>
+          <t>1990392</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011326</t>
+          <t>1990392</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>305046</t>
+          <t>354178</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>283145</t>
+          <t>329362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>326710</t>
+          <t>378979</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>551388</t>
+          <t>486795</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>511508</t>
+          <t>462161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>627954</t>
+          <t>511365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>856434</t>
+          <t>840973</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>808744</t>
+          <t>808518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>930972</t>
+          <t>876647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>168970</t>
+          <t>212704</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147306</t>
+          <t>187903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190871</t>
+          <t>237520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>288588</t>
+          <t>341967</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>212022</t>
+          <t>317397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>328468</t>
+          <t>366601</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>457558</t>
+          <t>554671</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383020</t>
+          <t>518997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505248</t>
+          <t>587126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>839976</t>
+          <t>828762</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>839976</t>
+          <t>828762</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>839976</t>
+          <t>828762</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313992</t>
+          <t>1395644</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313992</t>
+          <t>1395644</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313992</t>
+          <t>1395644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>181137</t>
+          <t>161379</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>137969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>199605</t>
+          <t>180075</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>470664</t>
+          <t>509483</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>445776</t>
+          <t>484260</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>496679</t>
+          <t>534642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>651801</t>
+          <t>670862</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>622306</t>
+          <t>633633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>685597</t>
+          <t>709730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>59206</t>
+          <t>74206</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40738</t>
+          <t>55510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81834</t>
+          <t>97616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>290106</t>
+          <t>334151</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264091</t>
+          <t>308992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>314994</t>
+          <t>359374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>349312</t>
+          <t>408357</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>315516</t>
+          <t>369489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>378807</t>
+          <t>445586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760770</t>
+          <t>843634</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760770</t>
+          <t>843634</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760770</t>
+          <t>843634</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001113</t>
+          <t>1079219</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001113</t>
+          <t>1079219</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001113</t>
+          <t>1079219</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2397192</t>
+          <t>2308945</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2301799</t>
+          <t>2256908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2638272</t>
+          <t>2371006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2479894</t>
+          <t>2366811</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2386584</t>
+          <t>2310627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2697624</t>
+          <t>2416027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4877085</t>
+          <t>4675756</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4721623</t>
+          <t>4590442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5134509</t>
+          <t>4750582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>973750</t>
+          <t>1126500</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>732670</t>
+          <t>1064439</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1069143</t>
+          <t>1178537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1090519</t>
+          <t>1259495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>872789</t>
+          <t>1210279</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1183829</t>
+          <t>1315679</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2064270</t>
+          <t>2385994</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1806846</t>
+          <t>2311168</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2219732</t>
+          <t>2471308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3370942</t>
+          <t>3435445</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3370942</t>
+          <t>3435445</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3370942</t>
+          <t>3435445</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3570413</t>
+          <t>3626306</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3570413</t>
+          <t>3626306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3570413</t>
+          <t>3626306</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6941355</t>
+          <t>7061750</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6941355</t>
+          <t>7061750</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6941355</t>
+          <t>7061750</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
